--- a/data/trans_camb/IP19C06-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C06-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-0.268316270089481</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.7680821807607717</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.945044008323867</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.16299351261669</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-1.108495227378136</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.9920392274105593</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-2.629699298103833</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.971757307387944</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.24737601087389</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-4.106672137874447</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-2.942919203391745</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-2.752306342740672</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>0.9956990145638041</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-0.6110708611376677</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1.128140618160663</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>-0.05785746213074221</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0.1942193972994946</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.3493327625745966</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.5979265803959338</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.8134233780397281</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.7279669587904762</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -705,9 +710,6 @@
       <c r="F8" s="6" t="inlineStr"/>
       <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -722,9 +724,6 @@
       <c r="F9" s="6" t="inlineStr"/>
       <c r="G9" s="6" t="inlineStr"/>
       <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +736,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-0.6500775780461719</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.6116182142162494</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.1839166599429786</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.5291548075748654</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.3941891000593263</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.07477797142944384</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +762,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-3.298973873397527</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.287818765723973</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.918464959229127</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.484093730703436</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-1.764463776810224</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-1.288719498380122</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +788,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.081188667962327</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.116290516591886</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.8180153544777666</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.8152031522200263</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>1.475572858535382</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +814,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.9408388088918351</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.1918415559641251</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.5519558786166121</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.4937202667252358</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.09365910927968485</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -811,9 +846,6 @@
       <c r="F14" s="6" t="inlineStr"/>
       <c r="G14" s="6" t="inlineStr"/>
       <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -828,9 +860,6 @@
       <c r="F15" s="6" t="inlineStr"/>
       <c r="G15" s="6" t="inlineStr"/>
       <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +872,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.7801198713508912</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2.933320289631332</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.3861233681538371</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1.275599251170297</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -862,13 +900,18 @@
       </c>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1.107340004809502</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.4779077055305557</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -879,13 +922,18 @@
       </c>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="n">
+        <v>3.984526880053288</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>6.363182076972014</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1.935670395883804</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>2.854466371047706</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -896,13 +944,26 @@
       </c>
       <c r="C19" s="6" t="inlineStr"/>
       <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -917,9 +978,6 @@
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr"/>
       <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -934,9 +992,6 @@
       <c r="F21" s="6" t="inlineStr"/>
       <c r="G21" s="6" t="inlineStr"/>
       <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1004,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>1.19279967755091</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0.5601806651979082</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -969,12 +1033,13 @@
       <c r="C23" s="5" t="inlineStr"/>
       <c r="D23" s="5" t="inlineStr"/>
       <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -986,12 +1051,13 @@
       <c r="C24" s="5" t="inlineStr"/>
       <c r="D24" s="5" t="inlineStr"/>
       <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="n">
+        <v>4.232349409645622</v>
+      </c>
       <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="n">
+        <v>2.393434105263191</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1003,12 +1069,17 @@
       <c r="C25" s="6" t="inlineStr"/>
       <c r="D25" s="6" t="inlineStr"/>
       <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
       <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1023,9 +1094,6 @@
       <c r="F26" s="6" t="inlineStr"/>
       <c r="G26" s="6" t="inlineStr"/>
       <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1040,9 +1108,6 @@
       <c r="F27" s="6" t="inlineStr"/>
       <c r="G27" s="6" t="inlineStr"/>
       <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1120,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-0.2537791764993754</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-0.0899256851576026</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.5593902349391888</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0.5515850981691353</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.4011106474783016</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0.188149982914231</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1146,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-1.1694298635528</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-0.9467804828421198</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-1.655068104910683</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-0.774400133729453</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-1.049426107550765</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-0.5429646464988751</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1172,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>0.3323966661088925</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0.7520611291888534</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.353826120370725</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>1.933783315033311</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.184579374723162</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0.9256758875489201</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1198,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.5692341961308882</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.2017059705540232</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.5912225536936945</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.58297326258188</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.5814933401023697</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0.2727625474238216</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1126,12 +1227,15 @@
       <c r="C32" s="6" t="inlineStr"/>
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="F32" s="6" t="n">
+        <v>-0.5509586935785601</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.5712143797351841</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1143,12 +1247,15 @@
       <c r="C33" s="6" t="inlineStr"/>
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="F33" s="6" t="n">
+        <v>4.899081741238032</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>1.307056926650516</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>2.764138530572416</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1266,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
